--- a/phase1_analysis/data/BD2025_dist_subset.xlsx
+++ b/phase1_analysis/data/BD2025_dist_subset.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D121"/>
+  <dimension ref="A1:D117"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -367,7 +367,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>pair_ID</t>
+          <t>audiomoth_ID</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -389,11 +389,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>100_pair23</t>
+          <t>Audiomoth_1</t>
         </is>
       </c>
       <c r="D2">
-        <v>110</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3">
@@ -409,11 +409,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>100_pair24</t>
+          <t>Audiomoth_10</t>
         </is>
       </c>
       <c r="D3">
-        <v>97</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4">
@@ -429,11 +429,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>100_pair25</t>
+          <t>Audiomoth_11</t>
         </is>
       </c>
       <c r="D4">
-        <v>110</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5">
@@ -449,11 +449,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>100_pair26</t>
+          <t>Audiomoth_12</t>
         </is>
       </c>
       <c r="D5">
-        <v>105</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6">
@@ -469,11 +469,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>100_pair27</t>
+          <t>Audiomoth_13</t>
         </is>
       </c>
       <c r="D6">
-        <v>105</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7">
@@ -489,11 +489,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>100_pair28</t>
+          <t>Audiomoth_14</t>
         </is>
       </c>
       <c r="D7">
-        <v>111</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8">
@@ -509,11 +509,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>100_pair29</t>
+          <t>Audiomoth_15</t>
         </is>
       </c>
       <c r="D8">
-        <v>110</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9">
@@ -529,11 +529,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>100_pair30</t>
+          <t>Audiomoth_16</t>
         </is>
       </c>
       <c r="D9">
-        <v>112</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10">
@@ -549,11 +549,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>100_pair31</t>
+          <t>Audiomoth_17</t>
         </is>
       </c>
       <c r="D10">
-        <v>110</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11">
@@ -569,11 +569,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>100_pair32</t>
+          <t>Audiomoth_18</t>
         </is>
       </c>
       <c r="D11">
-        <v>109</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12">
@@ -589,11 +589,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>100_pair33</t>
+          <t>Audiomoth_2</t>
         </is>
       </c>
       <c r="D12">
-        <v>104</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13">
@@ -609,11 +609,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>100_pair34</t>
+          <t>Audiomoth_20</t>
         </is>
       </c>
       <c r="D13">
-        <v>101</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14">
@@ -629,11 +629,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>100_pair35</t>
+          <t>Audiomoth_3</t>
         </is>
       </c>
       <c r="D14">
-        <v>105</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15">
@@ -649,11 +649,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>100_pair36</t>
+          <t>Audiomoth_4</t>
         </is>
       </c>
       <c r="D15">
-        <v>109</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -669,11 +669,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>100_pair37</t>
+          <t>Audiomoth_5</t>
         </is>
       </c>
       <c r="D16">
-        <v>103</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17">
@@ -689,11 +689,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>100_pair38</t>
+          <t>Audiomoth_6</t>
         </is>
       </c>
       <c r="D17">
-        <v>109</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
@@ -709,11 +709,11 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>100_pair39</t>
+          <t>Audiomoth_7</t>
         </is>
       </c>
       <c r="D18">
-        <v>113</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19">
@@ -729,11 +729,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>100_pair1</t>
+          <t>Audiomoth_1</t>
         </is>
       </c>
       <c r="D19">
-        <v>105</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20">
@@ -749,11 +749,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>100_pair10</t>
+          <t>Audiomoth_10</t>
         </is>
       </c>
       <c r="D20">
-        <v>89</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21">
@@ -769,11 +769,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>100_pair11</t>
+          <t>Audiomoth_11</t>
         </is>
       </c>
       <c r="D21">
-        <v>93</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22">
@@ -789,11 +789,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>100_pair12</t>
+          <t>Audiomoth_12</t>
         </is>
       </c>
       <c r="D22">
-        <v>123</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23">
@@ -809,11 +809,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>100_pair13</t>
+          <t>Audiomoth_13</t>
         </is>
       </c>
       <c r="D23">
-        <v>118</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24">
@@ -829,11 +829,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>100_pair14</t>
+          <t>Audiomoth_14</t>
         </is>
       </c>
       <c r="D24">
-        <v>114</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25">
@@ -849,11 +849,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>100_pair15</t>
+          <t>Audiomoth_15</t>
         </is>
       </c>
       <c r="D25">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26">
@@ -869,11 +869,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>100_pair16</t>
+          <t>Audiomoth_16</t>
         </is>
       </c>
       <c r="D26">
-        <v>99</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27">
@@ -889,11 +889,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>100_pair17</t>
+          <t>Audiomoth_17</t>
         </is>
       </c>
       <c r="D27">
-        <v>92</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28">
@@ -909,11 +909,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>100_pair18</t>
+          <t>Audiomoth_18</t>
         </is>
       </c>
       <c r="D28">
-        <v>106</v>
+        <v>93</v>
       </c>
     </row>
     <row r="29">
@@ -929,11 +929,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>100_pair19</t>
+          <t>Audiomoth_19</t>
         </is>
       </c>
       <c r="D29">
-        <v>100</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30">
@@ -949,11 +949,11 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>100_pair2</t>
+          <t>Audiomoth_2</t>
         </is>
       </c>
       <c r="D30">
-        <v>110</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31">
@@ -969,11 +969,11 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>100_pair20</t>
+          <t>Audiomoth_20</t>
         </is>
       </c>
       <c r="D31">
-        <v>101</v>
+        <v>64</v>
       </c>
     </row>
     <row r="32">
@@ -989,11 +989,11 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>100_pair21</t>
+          <t>Audiomoth_3</t>
         </is>
       </c>
       <c r="D32">
-        <v>101</v>
+        <v>73</v>
       </c>
     </row>
     <row r="33">
@@ -1009,11 +1009,11 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>100_pair22</t>
+          <t>Audiomoth_4</t>
         </is>
       </c>
       <c r="D33">
-        <v>116</v>
+        <v>85</v>
       </c>
     </row>
     <row r="34">
@@ -1029,11 +1029,11 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>100_pair3</t>
+          <t>Audiomoth_5</t>
         </is>
       </c>
       <c r="D34">
-        <v>113</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35">
@@ -1049,11 +1049,11 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>100_pair4</t>
+          <t>Audiomoth_6</t>
         </is>
       </c>
       <c r="D35">
-        <v>109</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36">
@@ -1069,11 +1069,11 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>100_pair5</t>
+          <t>Audiomoth_7</t>
         </is>
       </c>
       <c r="D36">
-        <v>104</v>
+        <v>64</v>
       </c>
     </row>
     <row r="37">
@@ -1089,11 +1089,11 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>100_pair6</t>
+          <t>Audiomoth_8</t>
         </is>
       </c>
       <c r="D37">
-        <v>103</v>
+        <v>65</v>
       </c>
     </row>
     <row r="38">
@@ -1109,51 +1109,51 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>100_pair7</t>
+          <t>Audiomoth_9</t>
         </is>
       </c>
       <c r="D38">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>dist_100</t>
+          <t>dist_150</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BDWD</t>
+          <t>BDMD</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>100_pair8</t>
+          <t>Audiomoth_11</t>
         </is>
       </c>
       <c r="D39">
-        <v>98</v>
+        <v>75</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>dist_100</t>
+          <t>dist_150</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BDWD</t>
+          <t>BDMD</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>100_pair9</t>
+          <t>Audiomoth_12</t>
         </is>
       </c>
       <c r="D40">
-        <v>101</v>
+        <v>71</v>
       </c>
     </row>
     <row r="41">
@@ -1169,11 +1169,11 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>150_pair14</t>
+          <t>Audiomoth_13</t>
         </is>
       </c>
       <c r="D41">
-        <v>103</v>
+        <v>77</v>
       </c>
     </row>
     <row r="42">
@@ -1189,11 +1189,11 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>150_pair15</t>
+          <t>Audiomoth_14</t>
         </is>
       </c>
       <c r="D42">
-        <v>108</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43">
@@ -1209,11 +1209,11 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>150_pair16</t>
+          <t>Audiomoth_15</t>
         </is>
       </c>
       <c r="D43">
-        <v>118</v>
+        <v>80</v>
       </c>
     </row>
     <row r="44">
@@ -1229,11 +1229,11 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>150_pair17</t>
+          <t>Audiomoth_16</t>
         </is>
       </c>
       <c r="D44">
-        <v>120</v>
+        <v>71</v>
       </c>
     </row>
     <row r="45">
@@ -1249,11 +1249,11 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>150_pair18</t>
+          <t>Audiomoth_17</t>
         </is>
       </c>
       <c r="D45">
-        <v>106</v>
+        <v>80</v>
       </c>
     </row>
     <row r="46">
@@ -1269,11 +1269,11 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>150_pair19</t>
+          <t>Audiomoth_2</t>
         </is>
       </c>
       <c r="D46">
-        <v>101</v>
+        <v>88</v>
       </c>
     </row>
     <row r="47">
@@ -1289,11 +1289,11 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>150_pair20</t>
+          <t>Audiomoth_20</t>
         </is>
       </c>
       <c r="D47">
-        <v>107</v>
+        <v>69</v>
       </c>
     </row>
     <row r="48">
@@ -1309,11 +1309,11 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>150_pair21</t>
+          <t>Audiomoth_4</t>
         </is>
       </c>
       <c r="D48">
-        <v>120</v>
+        <v>81</v>
       </c>
     </row>
     <row r="49">
@@ -1324,16 +1324,16 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BDWD</t>
+          <t>BDMD</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>150_pair1</t>
+          <t>Audiomoth_5</t>
         </is>
       </c>
       <c r="D49">
-        <v>111</v>
+        <v>77</v>
       </c>
     </row>
     <row r="50">
@@ -1344,16 +1344,16 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BDWD</t>
+          <t>BDMD</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>150_pair10</t>
+          <t>Audiomoth_6</t>
         </is>
       </c>
       <c r="D50">
-        <v>92</v>
+        <v>80</v>
       </c>
     </row>
     <row r="51">
@@ -1364,16 +1364,16 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BDWD</t>
+          <t>BDMD</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>150_pair11</t>
+          <t>Audiomoth_7</t>
         </is>
       </c>
       <c r="D51">
-        <v>110</v>
+        <v>75</v>
       </c>
     </row>
     <row r="52">
@@ -1389,11 +1389,11 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>150_pair12</t>
+          <t>Audiomoth_1</t>
         </is>
       </c>
       <c r="D52">
-        <v>108</v>
+        <v>67</v>
       </c>
     </row>
     <row r="53">
@@ -1409,11 +1409,11 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>150_pair13</t>
+          <t>Audiomoth_10</t>
         </is>
       </c>
       <c r="D53">
-        <v>123</v>
+        <v>80</v>
       </c>
     </row>
     <row r="54">
@@ -1429,11 +1429,11 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>150_pair2</t>
+          <t>Audiomoth_12</t>
         </is>
       </c>
       <c r="D54">
-        <v>110</v>
+        <v>87</v>
       </c>
     </row>
     <row r="55">
@@ -1449,11 +1449,11 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>150_pair3</t>
+          <t>Audiomoth_13</t>
         </is>
       </c>
       <c r="D55">
-        <v>108</v>
+        <v>78</v>
       </c>
     </row>
     <row r="56">
@@ -1469,11 +1469,11 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>150_pair4</t>
+          <t>Audiomoth_14</t>
         </is>
       </c>
       <c r="D56">
-        <v>108</v>
+        <v>80</v>
       </c>
     </row>
     <row r="57">
@@ -1489,11 +1489,11 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>150_pair5</t>
+          <t>Audiomoth_15</t>
         </is>
       </c>
       <c r="D57">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
     <row r="58">
@@ -1509,11 +1509,11 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>150_pair6</t>
+          <t>Audiomoth_16</t>
         </is>
       </c>
       <c r="D58">
-        <v>104</v>
+        <v>81</v>
       </c>
     </row>
     <row r="59">
@@ -1529,11 +1529,11 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>150_pair7</t>
+          <t>Audiomoth_18</t>
         </is>
       </c>
       <c r="D59">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="60">
@@ -1549,11 +1549,11 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>150_pair8</t>
+          <t>Audiomoth_19</t>
         </is>
       </c>
       <c r="D60">
-        <v>114</v>
+        <v>85</v>
       </c>
     </row>
     <row r="61">
@@ -1569,57 +1569,57 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>150_pair9</t>
+          <t>Audiomoth_2</t>
         </is>
       </c>
       <c r="D61">
-        <v>107</v>
+        <v>79</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>dist_200</t>
+          <t>dist_150</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BDMD</t>
+          <t>BDWD</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>200_pair5</t>
+          <t>Audiomoth_20</t>
         </is>
       </c>
       <c r="D62">
-        <v>116</v>
+        <v>64</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>dist_200</t>
+          <t>dist_150</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BDMD</t>
+          <t>BDWD</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>200_pair6</t>
+          <t>Audiomoth_3</t>
         </is>
       </c>
       <c r="D63">
-        <v>108</v>
+        <v>73</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>dist_200</t>
+          <t>dist_150</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1629,17 +1629,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>200_pair1</t>
+          <t>Audiomoth_4</t>
         </is>
       </c>
       <c r="D64">
-        <v>111</v>
+        <v>85</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>dist_200</t>
+          <t>dist_150</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1649,17 +1649,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>200_pair2</t>
+          <t>Audiomoth_5</t>
         </is>
       </c>
       <c r="D65">
-        <v>109</v>
+        <v>88</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>dist_200</t>
+          <t>dist_150</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1669,17 +1669,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>200_pair3</t>
+          <t>Audiomoth_6</t>
         </is>
       </c>
       <c r="D66">
-        <v>117</v>
+        <v>79</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>dist_200</t>
+          <t>dist_150</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1689,57 +1689,57 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>200_pair4</t>
+          <t>Audiomoth_7</t>
         </is>
       </c>
       <c r="D67">
-        <v>119</v>
+        <v>64</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>dist_50</t>
+          <t>dist_150</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BDMD</t>
+          <t>BDWD</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>50_pair32</t>
+          <t>Audiomoth_8</t>
         </is>
       </c>
       <c r="D68">
-        <v>105</v>
+        <v>65</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>dist_50</t>
+          <t>dist_150</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BDMD</t>
+          <t>BDWD</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>50_pair33</t>
+          <t>Audiomoth_9</t>
         </is>
       </c>
       <c r="D69">
-        <v>110</v>
+        <v>91</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>dist_50</t>
+          <t>dist_200</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1749,17 +1749,17 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>50_pair34</t>
+          <t>Audiomoth_16</t>
         </is>
       </c>
       <c r="D70">
-        <v>108</v>
+        <v>71</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>dist_50</t>
+          <t>dist_200</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1769,17 +1769,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>50_pair35</t>
+          <t>Audiomoth_2</t>
         </is>
       </c>
       <c r="D71">
-        <v>103</v>
+        <v>88</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>dist_50</t>
+          <t>dist_200</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1789,17 +1789,17 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>50_pair36</t>
+          <t>Audiomoth_3</t>
         </is>
       </c>
       <c r="D72">
-        <v>104</v>
+        <v>83</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>dist_50</t>
+          <t>dist_200</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1809,171 +1809,171 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>50_pair37</t>
+          <t>Audiomoth_5</t>
         </is>
       </c>
       <c r="D73">
-        <v>102</v>
+        <v>77</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>dist_50</t>
+          <t>dist_200</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BDMD</t>
+          <t>BDWD</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>50_pair38</t>
+          <t>Audiomoth_14</t>
         </is>
       </c>
       <c r="D74">
-        <v>102</v>
+        <v>80</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>dist_50</t>
+          <t>dist_200</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BDMD</t>
+          <t>BDWD</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>50_pair39</t>
+          <t>Audiomoth_15</t>
         </is>
       </c>
       <c r="D75">
-        <v>106</v>
+        <v>97</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>dist_50</t>
+          <t>dist_200</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BDMD</t>
+          <t>BDWD</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>50_pair40</t>
+          <t>Audiomoth_16</t>
         </is>
       </c>
       <c r="D76">
-        <v>101</v>
+        <v>81</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>dist_50</t>
+          <t>dist_200</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BDMD</t>
+          <t>BDWD</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>50_pair41</t>
+          <t>Audiomoth_18</t>
         </is>
       </c>
       <c r="D77">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>dist_50</t>
+          <t>dist_200</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BDMD</t>
+          <t>BDWD</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>50_pair42</t>
+          <t>Audiomoth_2</t>
         </is>
       </c>
       <c r="D78">
-        <v>115</v>
+        <v>79</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>dist_50</t>
+          <t>dist_200</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BDMD</t>
+          <t>BDWD</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>50_pair43</t>
+          <t>Audiomoth_3</t>
         </is>
       </c>
       <c r="D79">
-        <v>121</v>
+        <v>73</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>dist_50</t>
+          <t>dist_200</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BDMD</t>
+          <t>BDWD</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>50_pair44</t>
+          <t>Audiomoth_4</t>
         </is>
       </c>
       <c r="D80">
-        <v>100</v>
+        <v>85</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>dist_50</t>
+          <t>dist_200</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BDMD</t>
+          <t>BDWD</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>50_pair45</t>
+          <t>Audiomoth_9</t>
         </is>
       </c>
       <c r="D81">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="82">
@@ -1989,11 +1989,11 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>50_pair46</t>
+          <t>Audiomoth_1</t>
         </is>
       </c>
       <c r="D82">
-        <v>106</v>
+        <v>74</v>
       </c>
     </row>
     <row r="83">
@@ -2009,11 +2009,11 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>50_pair47</t>
+          <t>Audiomoth_10</t>
         </is>
       </c>
       <c r="D83">
-        <v>108</v>
+        <v>84</v>
       </c>
     </row>
     <row r="84">
@@ -2029,11 +2029,11 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>50_pair48</t>
+          <t>Audiomoth_11</t>
         </is>
       </c>
       <c r="D84">
-        <v>102</v>
+        <v>75</v>
       </c>
     </row>
     <row r="85">
@@ -2049,11 +2049,11 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>50_pair49</t>
+          <t>Audiomoth_12</t>
         </is>
       </c>
       <c r="D85">
-        <v>99</v>
+        <v>71</v>
       </c>
     </row>
     <row r="86">
@@ -2069,11 +2069,11 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>50_pair50</t>
+          <t>Audiomoth_13</t>
         </is>
       </c>
       <c r="D86">
-        <v>99</v>
+        <v>77</v>
       </c>
     </row>
     <row r="87">
@@ -2089,11 +2089,11 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>50_pair51</t>
+          <t>Audiomoth_14</t>
         </is>
       </c>
       <c r="D87">
-        <v>103</v>
+        <v>82</v>
       </c>
     </row>
     <row r="88">
@@ -2109,11 +2109,11 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>50_pair52</t>
+          <t>Audiomoth_15</t>
         </is>
       </c>
       <c r="D88">
-        <v>108</v>
+        <v>80</v>
       </c>
     </row>
     <row r="89">
@@ -2129,11 +2129,11 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>50_pair53</t>
+          <t>Audiomoth_16</t>
         </is>
       </c>
       <c r="D89">
-        <v>106</v>
+        <v>71</v>
       </c>
     </row>
     <row r="90">
@@ -2149,11 +2149,11 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>50_pair54</t>
+          <t>Audiomoth_17</t>
         </is>
       </c>
       <c r="D90">
-        <v>110</v>
+        <v>80</v>
       </c>
     </row>
     <row r="91">
@@ -2164,16 +2164,16 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>BDWD</t>
+          <t>BDMD</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>50_pair1</t>
+          <t>Audiomoth_18</t>
         </is>
       </c>
       <c r="D91">
-        <v>105</v>
+        <v>61</v>
       </c>
     </row>
     <row r="92">
@@ -2184,12 +2184,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BDWD</t>
+          <t>BDMD</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>50_pair10</t>
+          <t>Audiomoth_2</t>
         </is>
       </c>
       <c r="D92">
@@ -2204,16 +2204,16 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BDWD</t>
+          <t>BDMD</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>50_pair11</t>
+          <t>Audiomoth_20</t>
         </is>
       </c>
       <c r="D93">
-        <v>85</v>
+        <v>69</v>
       </c>
     </row>
     <row r="94">
@@ -2224,16 +2224,16 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BDWD</t>
+          <t>BDMD</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>50_pair12</t>
+          <t>Audiomoth_4</t>
         </is>
       </c>
       <c r="D94">
-        <v>110</v>
+        <v>81</v>
       </c>
     </row>
     <row r="95">
@@ -2244,16 +2244,16 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>BDWD</t>
+          <t>BDMD</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>50_pair13</t>
+          <t>Audiomoth_5</t>
         </is>
       </c>
       <c r="D95">
-        <v>102</v>
+        <v>77</v>
       </c>
     </row>
     <row r="96">
@@ -2264,16 +2264,16 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>BDWD</t>
+          <t>BDMD</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>50_pair14</t>
+          <t>Audiomoth_6</t>
         </is>
       </c>
       <c r="D96">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="97">
@@ -2284,16 +2284,16 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>BDWD</t>
+          <t>BDMD</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>50_pair15</t>
+          <t>Audiomoth_7</t>
         </is>
       </c>
       <c r="D97">
-        <v>97</v>
+        <v>75</v>
       </c>
     </row>
     <row r="98">
@@ -2309,11 +2309,11 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>50_pair16</t>
+          <t>Audiomoth_1</t>
         </is>
       </c>
       <c r="D98">
-        <v>118</v>
+        <v>67</v>
       </c>
     </row>
     <row r="99">
@@ -2329,11 +2329,11 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>50_pair17</t>
+          <t>Audiomoth_10</t>
         </is>
       </c>
       <c r="D99">
-        <v>113</v>
+        <v>80</v>
       </c>
     </row>
     <row r="100">
@@ -2349,11 +2349,11 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>50_pair18</t>
+          <t>Audiomoth_11</t>
         </is>
       </c>
       <c r="D100">
-        <v>122</v>
+        <v>73</v>
       </c>
     </row>
     <row r="101">
@@ -2369,11 +2369,11 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>50_pair19</t>
+          <t>Audiomoth_12</t>
         </is>
       </c>
       <c r="D101">
-        <v>114</v>
+        <v>87</v>
       </c>
     </row>
     <row r="102">
@@ -2389,11 +2389,11 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>50_pair2</t>
+          <t>Audiomoth_13</t>
         </is>
       </c>
       <c r="D102">
-        <v>110</v>
+        <v>78</v>
       </c>
     </row>
     <row r="103">
@@ -2409,11 +2409,11 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>50_pair20</t>
+          <t>Audiomoth_14</t>
         </is>
       </c>
       <c r="D103">
-        <v>109</v>
+        <v>80</v>
       </c>
     </row>
     <row r="104">
@@ -2429,11 +2429,11 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>50_pair21</t>
+          <t>Audiomoth_15</t>
         </is>
       </c>
       <c r="D104">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="105">
@@ -2449,11 +2449,11 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>50_pair22</t>
+          <t>Audiomoth_16</t>
         </is>
       </c>
       <c r="D105">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="106">
@@ -2469,11 +2469,11 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>50_pair23</t>
+          <t>Audiomoth_17</t>
         </is>
       </c>
       <c r="D106">
-        <v>93</v>
+        <v>67</v>
       </c>
     </row>
     <row r="107">
@@ -2489,11 +2489,11 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>50_pair24</t>
+          <t>Audiomoth_18</t>
         </is>
       </c>
       <c r="D107">
-        <v>86</v>
+        <v>93</v>
       </c>
     </row>
     <row r="108">
@@ -2509,11 +2509,11 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>50_pair25</t>
+          <t>Audiomoth_19</t>
         </is>
       </c>
       <c r="D108">
-        <v>103</v>
+        <v>85</v>
       </c>
     </row>
     <row r="109">
@@ -2529,11 +2529,11 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>50_pair26</t>
+          <t>Audiomoth_2</t>
         </is>
       </c>
       <c r="D109">
-        <v>94</v>
+        <v>79</v>
       </c>
     </row>
     <row r="110">
@@ -2549,11 +2549,11 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>50_pair27</t>
+          <t>Audiomoth_20</t>
         </is>
       </c>
       <c r="D110">
-        <v>86</v>
+        <v>64</v>
       </c>
     </row>
     <row r="111">
@@ -2569,11 +2569,11 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>50_pair28</t>
+          <t>Audiomoth_3</t>
         </is>
       </c>
       <c r="D111">
-        <v>102</v>
+        <v>73</v>
       </c>
     </row>
     <row r="112">
@@ -2589,11 +2589,11 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>50_pair29</t>
+          <t>Audiomoth_4</t>
         </is>
       </c>
       <c r="D112">
-        <v>92</v>
+        <v>85</v>
       </c>
     </row>
     <row r="113">
@@ -2609,11 +2609,11 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>50_pair3</t>
+          <t>Audiomoth_5</t>
         </is>
       </c>
       <c r="D113">
-        <v>113</v>
+        <v>88</v>
       </c>
     </row>
     <row r="114">
@@ -2629,11 +2629,11 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>50_pair30</t>
+          <t>Audiomoth_6</t>
         </is>
       </c>
       <c r="D114">
-        <v>94</v>
+        <v>79</v>
       </c>
     </row>
     <row r="115">
@@ -2649,11 +2649,11 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>50_pair31</t>
+          <t>Audiomoth_7</t>
         </is>
       </c>
       <c r="D115">
-        <v>117</v>
+        <v>64</v>
       </c>
     </row>
     <row r="116">
@@ -2669,11 +2669,11 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>50_pair4</t>
+          <t>Audiomoth_8</t>
         </is>
       </c>
       <c r="D116">
-        <v>109</v>
+        <v>65</v>
       </c>
     </row>
     <row r="117">
@@ -2689,91 +2689,11 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>50_pair5</t>
+          <t>Audiomoth_9</t>
         </is>
       </c>
       <c r="D117">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>dist_50</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>BDWD</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>50_pair6</t>
-        </is>
-      </c>
-      <c r="D118">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>dist_50</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>BDWD</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>50_pair7</t>
-        </is>
-      </c>
-      <c r="D119">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>dist_50</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>BDWD</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>50_pair8</t>
-        </is>
-      </c>
-      <c r="D120">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>dist_50</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>BDWD</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>50_pair9</t>
-        </is>
-      </c>
-      <c r="D121">
-        <v>101</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
